--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_Auto.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_Auto.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1260</v>
+        <v>1448</v>
       </c>
       <c r="C2">
-        <v>1636</v>
+        <v>1740</v>
       </c>
       <c r="D2">
-        <v>1915</v>
+        <v>1958</v>
       </c>
       <c r="E2">
-        <v>2020</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1117</v>
+        <v>1493</v>
       </c>
       <c r="C3">
-        <v>1532</v>
+        <v>1791</v>
       </c>
       <c r="D3">
-        <v>1839</v>
+        <v>2020</v>
       </c>
       <c r="E3">
-        <v>2006</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1091</v>
+        <v>1484</v>
       </c>
       <c r="C4">
-        <v>1518</v>
+        <v>1777</v>
       </c>
       <c r="D4">
-        <v>1832</v>
+        <v>2009</v>
       </c>
       <c r="E4">
-        <v>2000</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1087</v>
+        <v>1459</v>
       </c>
       <c r="C5">
-        <v>1514</v>
+        <v>1759</v>
       </c>
       <c r="D5">
-        <v>1832</v>
+        <v>1989</v>
       </c>
       <c r="E5">
-        <v>2002</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1074</v>
+        <v>1701</v>
       </c>
       <c r="C6">
-        <v>1515</v>
+        <v>1934</v>
       </c>
       <c r="D6">
-        <v>1839</v>
+        <v>2064</v>
       </c>
       <c r="E6">
-        <v>2010</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1090</v>
+        <v>1424</v>
       </c>
       <c r="C7">
-        <v>1517</v>
+        <v>1744</v>
       </c>
       <c r="D7">
-        <v>1834</v>
+        <v>1997</v>
       </c>
       <c r="E7">
-        <v>2003</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1067</v>
+        <v>1735</v>
       </c>
       <c r="C8">
-        <v>1509</v>
+        <v>1924</v>
       </c>
       <c r="D8">
-        <v>1833</v>
+        <v>2059</v>
       </c>
       <c r="E8">
-        <v>2005</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1076</v>
+        <v>1462</v>
       </c>
       <c r="C9">
-        <v>1506</v>
+        <v>1752</v>
       </c>
       <c r="D9">
-        <v>1826</v>
+        <v>1977</v>
       </c>
       <c r="E9">
-        <v>1996</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1151</v>
+        <v>1317</v>
       </c>
       <c r="C10">
-        <v>1581</v>
+        <v>1668</v>
       </c>
       <c r="D10">
-        <v>1895</v>
+        <v>1927</v>
       </c>
       <c r="E10">
-        <v>2008</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1229</v>
+        <v>1375</v>
       </c>
       <c r="C11">
-        <v>1631</v>
+        <v>1704</v>
       </c>
       <c r="D11">
-        <v>1921</v>
+        <v>1950</v>
       </c>
       <c r="E11">
-        <v>2025</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1064</v>
+        <v>1166</v>
       </c>
       <c r="C12">
-        <v>1514</v>
+        <v>1584</v>
       </c>
       <c r="D12">
-        <v>1857</v>
+        <v>1889</v>
       </c>
       <c r="E12">
-        <v>1984</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1134</v>
+        <v>1285</v>
       </c>
       <c r="C13">
-        <v>1566</v>
+        <v>1649</v>
       </c>
       <c r="D13">
-        <v>1885</v>
+        <v>1917</v>
       </c>
       <c r="E13">
-        <v>2000</v>
+        <v>2012</v>
       </c>
     </row>
   </sheetData>
